--- a/测试集.xlsx
+++ b/测试集.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\深圳大学项目\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rag_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D36749E-8174-40C3-A19E-466FAADD4739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1272F6C-9F11-4170-8542-C9F37DAE2470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2310" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="定义类" sheetId="1" r:id="rId1"/>
